--- a/6098.T_report.xlsx
+++ b/6098.T_report.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J5"/>
+  <dimension ref="A1:M10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -449,10 +449,30 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
+          <t>手数料込み利益率(%)</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>手数料(円)</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>決済後資産(円)</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
           <t>保有日数</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>決済理由</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
         <is>
           <t>バックテスト結果</t>
         </is>
@@ -464,68 +484,428 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2023-08-30</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2023-09-13</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>7308</v>
+        <v>4989.25</v>
       </c>
       <c r="E2" t="n">
-        <v>12770</v>
+        <v>5007.95</v>
       </c>
       <c r="F2" t="n">
-        <v>74.73999999999999</v>
+        <v>0.37</v>
       </c>
       <c r="G2" t="n">
-        <v>88</v>
-      </c>
-      <c r="I2" t="inlineStr">
+        <v>0.17</v>
+      </c>
+      <c r="H2" t="n">
+        <v>2004</v>
+      </c>
+      <c r="I2" t="n">
+        <v>1001745</v>
+      </c>
+      <c r="J2" t="n">
+        <v>14</v>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>atr_stop</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
         <is>
           <t>総取引回数</t>
         </is>
       </c>
-      <c r="J2" t="n">
-        <v>1</v>
+      <c r="M2" t="n">
+        <v>9</v>
       </c>
     </row>
     <row r="3">
-      <c r="I3" t="inlineStr">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2024-02-29</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>2024-03-11</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>6002.51</v>
+      </c>
+      <c r="E3" t="n">
+        <v>6358.23</v>
+      </c>
+      <c r="F3" t="n">
+        <v>5.93</v>
+      </c>
+      <c r="G3" t="n">
+        <v>5.72</v>
+      </c>
+      <c r="H3" t="n">
+        <v>2063</v>
+      </c>
+      <c r="I3" t="n">
+        <v>1059049</v>
+      </c>
+      <c r="J3" t="n">
+        <v>11</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>take_profit</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
         <is>
           <t>勝率</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>100.0%</t>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="I4" t="inlineStr">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2024-05-08</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>2024-05-16</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>7000.74</v>
+      </c>
+      <c r="E4" t="n">
+        <v>7654.94</v>
+      </c>
+      <c r="F4" t="n">
+        <v>9.34</v>
+      </c>
+      <c r="G4" t="n">
+        <v>9.140000000000001</v>
+      </c>
+      <c r="H4" t="n">
+        <v>2217</v>
+      </c>
+      <c r="I4" t="n">
+        <v>1155798</v>
+      </c>
+      <c r="J4" t="n">
+        <v>8</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>take_profit</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
         <is>
           <t>総利益率</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>74.74%</t>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>38.46%</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="I5" t="inlineStr">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2024-06-05</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>2024-06-26</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>7816.51</v>
+      </c>
+      <c r="E5" t="n">
+        <v>8469.08</v>
+      </c>
+      <c r="F5" t="n">
+        <v>8.35</v>
+      </c>
+      <c r="G5" t="n">
+        <v>8.140000000000001</v>
+      </c>
+      <c r="H5" t="n">
+        <v>2408</v>
+      </c>
+      <c r="I5" t="n">
+        <v>1249884</v>
+      </c>
+      <c r="J5" t="n">
+        <v>21</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>take_profit</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
         <is>
           <t>平均保有日数</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>88.0日</t>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>7.7日</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2024-11-12</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>2024-11-13</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>10270.02</v>
+      </c>
+      <c r="E6" t="n">
+        <v>9853.84</v>
+      </c>
+      <c r="F6" t="n">
+        <v>-4.05</v>
+      </c>
+      <c r="G6" t="n">
+        <v>-4.25</v>
+      </c>
+      <c r="H6" t="n">
+        <v>2449</v>
+      </c>
+      <c r="I6" t="n">
+        <v>1196784</v>
+      </c>
+      <c r="J6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>stop_loss</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>最終資産</t>
+        </is>
+      </c>
+      <c r="M6" t="n">
+        <v>1384620</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2025-07-23</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>2025-07-28</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>8398.5</v>
+      </c>
+      <c r="E7" t="n">
+        <v>9009.93</v>
+      </c>
+      <c r="F7" t="n">
+        <v>7.28</v>
+      </c>
+      <c r="G7" t="n">
+        <v>7.07</v>
+      </c>
+      <c r="H7" t="n">
+        <v>2481</v>
+      </c>
+      <c r="I7" t="n">
+        <v>1281431</v>
+      </c>
+      <c r="J7" t="n">
+        <v>5</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>take_profit</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>手数料込み利益</t>
+        </is>
+      </c>
+      <c r="M7" t="n">
+        <v>384620</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>8558.110000000001</v>
+      </c>
+      <c r="E8" t="n">
+        <v>8244.34</v>
+      </c>
+      <c r="F8" t="n">
+        <v>-3.67</v>
+      </c>
+      <c r="G8" t="n">
+        <v>-3.86</v>
+      </c>
+      <c r="H8" t="n">
+        <v>2516</v>
+      </c>
+      <c r="I8" t="n">
+        <v>1231932</v>
+      </c>
+      <c r="J8" t="n">
+        <v>3</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>stop_loss</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>総手数料</t>
+        </is>
+      </c>
+      <c r="M8" t="n">
+        <v>21130</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>9264.389999999999</v>
+      </c>
+      <c r="E9" t="n">
+        <v>8933.27</v>
+      </c>
+      <c r="F9" t="n">
+        <v>-3.57</v>
+      </c>
+      <c r="G9" t="n">
+        <v>-3.77</v>
+      </c>
+      <c r="H9" t="n">
+        <v>2420</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1185482</v>
+      </c>
+      <c r="J9" t="n">
+        <v>2</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>stop_loss</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>7787.78</v>
+      </c>
+      <c r="E10" t="n">
+        <v>9112.879999999999</v>
+      </c>
+      <c r="F10" t="n">
+        <v>17.02</v>
+      </c>
+      <c r="G10" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="H10" t="n">
+        <v>2573</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1384620</v>
+      </c>
+      <c r="J10" t="n">
+        <v>4</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>take_profit</t>
         </is>
       </c>
     </row>

--- a/6098.T_report.xlsx
+++ b/6098.T_report.xlsx
@@ -557,7 +557,7 @@
         <v>2063</v>
       </c>
       <c r="I3" t="n">
-        <v>1059049</v>
+        <v>1059048</v>
       </c>
       <c r="J3" t="n">
         <v>11</v>
@@ -593,7 +593,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>7000.74</v>
+        <v>7000.73</v>
       </c>
       <c r="E4" t="n">
         <v>7654.94</v>
@@ -647,7 +647,7 @@
         <v>7816.51</v>
       </c>
       <c r="E5" t="n">
-        <v>8469.08</v>
+        <v>8469.09</v>
       </c>
       <c r="F5" t="n">
         <v>8.35</v>
@@ -796,7 +796,7 @@
         <v>8558.110000000001</v>
       </c>
       <c r="E8" t="n">
-        <v>8244.34</v>
+        <v>8244.33</v>
       </c>
       <c r="F8" t="n">
         <v>-3.67</v>
